--- a/data/source/stockbook.xlsx
+++ b/data/source/stockbook.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.8.200\Yohan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11595" tabRatio="604" firstSheet="17" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11595" tabRatio="604" firstSheet="14" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="Summery" sheetId="18" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1955" uniqueCount="536">
   <si>
     <t>Edward &amp; Christie(Pvt)Ltd</t>
   </si>
@@ -1650,6 +1650,24 @@
   </si>
   <si>
     <t>Batticoloa LOT/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+  </si>
+  <si>
+    <t>LO-8348</t>
+  </si>
+  <si>
+    <t>ZB-1568 (Gampaha)</t>
+  </si>
+  <si>
+    <t>VR-70</t>
+  </si>
+  <si>
+    <t>Baticoloa Lot 2</t>
+  </si>
+  <si>
+    <t>SL-01</t>
   </si>
 </sst>
 </file>
@@ -2277,13 +2295,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2292,20 +2313,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2352,6 +2370,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2843,11 +2862,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="487363240"/>
-        <c:axId val="487362064"/>
+        <c:axId val="353907072"/>
+        <c:axId val="353949456"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="487363240"/>
+        <c:axId val="353907072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2889,7 +2908,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487362064"/>
+        <c:crossAx val="353949456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2897,7 +2916,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="487362064"/>
+        <c:axId val="353949456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2948,7 +2967,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487363240"/>
+        <c:crossAx val="353907072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2962,6 +2981,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3584,7 +3604,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3949,7 +3969,7 @@
       </c>
       <c r="D4" s="65">
         <f>'15W40(CI-04)Valvoline'!$G$277</f>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="E4" s="46"/>
     </row>
@@ -4031,7 +4051,7 @@
       </c>
       <c r="D10" s="65">
         <f>'HD-68 Hy-Oil Caltex'!$G$312</f>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="E10" s="46"/>
     </row>
@@ -4083,7 +4103,7 @@
       </c>
       <c r="D14" s="65">
         <f>'Power Oil-1888'!$G$110</f>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="E14" s="46"/>
     </row>
@@ -4125,7 +4145,7 @@
       </c>
       <c r="D17" s="65">
         <f>'80W90 G-Oil (Servo)'!$G$62</f>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="E17" s="46"/>
     </row>
@@ -4151,7 +4171,7 @@
       </c>
       <c r="D19" s="65">
         <f>Grease!$G$201</f>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="E19" s="46"/>
       <c r="M19" s="31" t="s">
@@ -4166,8 +4186,8 @@
         <v>522</v>
       </c>
       <c r="D20" s="65">
-        <f>'K-Oil'!$G$324</f>
-        <v>3</v>
+        <f>'K-Oil'!$G$328</f>
+        <v>0</v>
       </c>
       <c r="E20" s="46"/>
     </row>
@@ -4180,7 +4200,7 @@
       </c>
       <c r="D21" s="65">
         <f>PETROL!$G$39</f>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="E21" s="46"/>
     </row>
@@ -4193,7 +4213,7 @@
       </c>
       <c r="D22" s="66">
         <f>'HUB GREASE'!$G$20</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="46"/>
     </row>
@@ -7174,28 +7194,40 @@
       <c r="H99" s="59"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="59"/>
+      <c r="A100" s="60">
+        <v>46180</v>
+      </c>
       <c r="B100" s="59"/>
       <c r="C100" s="59"/>
-      <c r="D100" s="59"/>
+      <c r="D100" s="59" t="s">
+        <v>134</v>
+      </c>
       <c r="E100" s="62"/>
-      <c r="F100" s="62"/>
+      <c r="F100" s="62">
+        <v>20</v>
+      </c>
       <c r="G100" s="62">
         <f>G99+E100-F100</f>
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="H100" s="59"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="59"/>
+      <c r="A101" s="60">
+        <v>46184</v>
+      </c>
       <c r="B101" s="59"/>
       <c r="C101" s="59"/>
-      <c r="D101" s="59"/>
+      <c r="D101" s="59" t="s">
+        <v>299</v>
+      </c>
       <c r="E101" s="62"/>
-      <c r="F101" s="62"/>
+      <c r="F101" s="62">
+        <v>0.5</v>
+      </c>
       <c r="G101" s="62">
         <f>G100+E101-F101</f>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H101" s="59"/>
     </row>
@@ -7208,7 +7240,7 @@
       <c r="F102" s="62"/>
       <c r="G102" s="62">
         <f t="shared" ref="G102:G110" si="6">G101+E102-F102</f>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H102" s="59"/>
     </row>
@@ -7221,7 +7253,7 @@
       <c r="F103" s="62"/>
       <c r="G103" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H103" s="59"/>
     </row>
@@ -7234,7 +7266,7 @@
       <c r="F104" s="62"/>
       <c r="G104" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H104" s="59"/>
     </row>
@@ -7247,7 +7279,7 @@
       <c r="F105" s="62"/>
       <c r="G105" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H105" s="59"/>
     </row>
@@ -7260,7 +7292,7 @@
       <c r="F106" s="62"/>
       <c r="G106" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H106" s="59"/>
     </row>
@@ -7273,7 +7305,7 @@
       <c r="F107" s="62"/>
       <c r="G107" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H107" s="59"/>
     </row>
@@ -7286,7 +7318,7 @@
       <c r="F108" s="62"/>
       <c r="G108" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H108" s="59"/>
     </row>
@@ -7299,7 +7331,7 @@
       <c r="F109" s="62"/>
       <c r="G109" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H109" s="59"/>
     </row>
@@ -7312,7 +7344,7 @@
       <c r="F110" s="62"/>
       <c r="G110" s="62">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>73.5</v>
       </c>
       <c r="H110" s="59"/>
     </row>
@@ -12303,15 +12335,21 @@
       <c r="H22" s="59"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="60"/>
+      <c r="A23" s="60">
+        <v>46185</v>
+      </c>
       <c r="B23" s="59"/>
       <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
+      <c r="D23" s="59" t="s">
+        <v>59</v>
+      </c>
       <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
+      <c r="F23" s="62">
+        <v>2</v>
+      </c>
       <c r="G23" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H23" s="59"/>
     </row>
@@ -12324,7 +12362,7 @@
       <c r="F24" s="62"/>
       <c r="G24" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H24" s="59"/>
     </row>
@@ -12337,7 +12375,7 @@
       <c r="F25" s="62"/>
       <c r="G25" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H25" s="59"/>
     </row>
@@ -12350,7 +12388,7 @@
       <c r="F26" s="62"/>
       <c r="G26" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H26" s="59"/>
     </row>
@@ -12363,7 +12401,7 @@
       <c r="F27" s="62"/>
       <c r="G27" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H27" s="59"/>
     </row>
@@ -12376,7 +12414,7 @@
       <c r="F28" s="62"/>
       <c r="G28" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H28" s="59"/>
     </row>
@@ -12389,7 +12427,7 @@
       <c r="F29" s="62"/>
       <c r="G29" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H29" s="59"/>
     </row>
@@ -12402,7 +12440,7 @@
       <c r="F30" s="62"/>
       <c r="G30" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H30" s="59"/>
     </row>
@@ -12415,7 +12453,7 @@
       <c r="F31" s="62"/>
       <c r="G31" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H31" s="59"/>
     </row>
@@ -12428,7 +12466,7 @@
       <c r="F32" s="62"/>
       <c r="G32" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H32" s="59"/>
     </row>
@@ -12441,7 +12479,7 @@
       <c r="F33" s="73"/>
       <c r="G33" s="73">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H33" s="72"/>
     </row>
@@ -12454,7 +12492,7 @@
       <c r="F34" s="80"/>
       <c r="G34" s="80">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H34" s="78"/>
     </row>
@@ -12467,7 +12505,7 @@
       <c r="F35" s="62"/>
       <c r="G35" s="73">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H35" s="59"/>
     </row>
@@ -12480,7 +12518,7 @@
       <c r="F36" s="62"/>
       <c r="G36" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H36" s="59"/>
     </row>
@@ -12493,7 +12531,7 @@
       <c r="F37" s="62"/>
       <c r="G37" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H37" s="59"/>
     </row>
@@ -12506,7 +12544,7 @@
       <c r="F38" s="62"/>
       <c r="G38" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H38" s="59"/>
     </row>
@@ -12519,7 +12557,7 @@
       <c r="F39" s="62"/>
       <c r="G39" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H39" s="59"/>
     </row>
@@ -12532,7 +12570,7 @@
       <c r="F40" s="62"/>
       <c r="G40" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H40" s="59"/>
     </row>
@@ -12545,7 +12583,7 @@
       <c r="F41" s="62"/>
       <c r="G41" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H41" s="59"/>
     </row>
@@ -12558,7 +12596,7 @@
       <c r="F42" s="62"/>
       <c r="G42" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H42" s="59"/>
     </row>
@@ -12571,7 +12609,7 @@
       <c r="F43" s="62"/>
       <c r="G43" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H43" s="59"/>
     </row>
@@ -12584,7 +12622,7 @@
       <c r="F44" s="62"/>
       <c r="G44" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H44" s="59"/>
     </row>
@@ -12597,7 +12635,7 @@
       <c r="F45" s="62"/>
       <c r="G45" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H45" s="59"/>
     </row>
@@ -12610,7 +12648,7 @@
       <c r="F46" s="62"/>
       <c r="G46" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H46" s="59"/>
     </row>
@@ -12623,7 +12661,7 @@
       <c r="F47" s="62"/>
       <c r="G47" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H47" s="59"/>
     </row>
@@ -12636,7 +12674,7 @@
       <c r="F48" s="62"/>
       <c r="G48" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H48" s="59"/>
     </row>
@@ -12649,7 +12687,7 @@
       <c r="F49" s="62"/>
       <c r="G49" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H49" s="59"/>
     </row>
@@ -12662,7 +12700,7 @@
       <c r="F50" s="62"/>
       <c r="G50" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H50" s="59"/>
     </row>
@@ -12677,7 +12715,7 @@
       <c r="F51" s="62"/>
       <c r="G51" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H51" s="59"/>
     </row>
@@ -12690,7 +12728,7 @@
       <c r="F52" s="62"/>
       <c r="G52" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H52" s="59"/>
     </row>
@@ -12703,7 +12741,7 @@
       <c r="F53" s="62"/>
       <c r="G53" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H53" s="59"/>
     </row>
@@ -12716,7 +12754,7 @@
       <c r="F54" s="62"/>
       <c r="G54" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H54" s="59"/>
     </row>
@@ -12729,7 +12767,7 @@
       <c r="F55" s="62"/>
       <c r="G55" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H55" s="59"/>
     </row>
@@ -12742,7 +12780,7 @@
       <c r="F56" s="62"/>
       <c r="G56" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H56" s="59"/>
     </row>
@@ -12755,7 +12793,7 @@
       <c r="F57" s="62"/>
       <c r="G57" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H57" s="59"/>
     </row>
@@ -12768,7 +12806,7 @@
       <c r="F58" s="62"/>
       <c r="G58" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H58" s="59"/>
     </row>
@@ -12781,7 +12819,7 @@
       <c r="F59" s="62"/>
       <c r="G59" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H59" s="59"/>
     </row>
@@ -12794,7 +12832,7 @@
       <c r="F60" s="62"/>
       <c r="G60" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H60" s="59"/>
     </row>
@@ -12807,7 +12845,7 @@
       <c r="F61" s="62"/>
       <c r="G61" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H61" s="59"/>
     </row>
@@ -12820,7 +12858,7 @@
       <c r="F62" s="62"/>
       <c r="G62" s="62">
         <f t="shared" si="0"/>
-        <v>63.5</v>
+        <v>61.5</v>
       </c>
       <c r="H62" s="59"/>
     </row>
@@ -17608,184 +17646,268 @@
       <c r="H182" s="27"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="39"/>
+      <c r="A183" s="39">
+        <v>46180</v>
+      </c>
       <c r="B183" s="27"/>
       <c r="C183" s="27"/>
-      <c r="D183" s="27"/>
+      <c r="D183" s="27" t="s">
+        <v>143</v>
+      </c>
       <c r="E183" s="42"/>
-      <c r="F183" s="42"/>
+      <c r="F183" s="42">
+        <v>2</v>
+      </c>
       <c r="G183" s="42">
         <f t="shared" si="16"/>
-        <v>203.25</v>
+        <v>201.25</v>
       </c>
       <c r="H183" s="27"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="39"/>
+      <c r="A184" s="39">
+        <v>46180</v>
+      </c>
       <c r="B184" s="27"/>
       <c r="C184" s="27"/>
-      <c r="D184" s="27"/>
+      <c r="D184" s="27" t="s">
+        <v>134</v>
+      </c>
       <c r="E184" s="42"/>
-      <c r="F184" s="42"/>
+      <c r="F184" s="42">
+        <v>15</v>
+      </c>
       <c r="G184" s="42">
         <f t="shared" si="16"/>
-        <v>203.25</v>
+        <v>186.25</v>
       </c>
       <c r="H184" s="27"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="39"/>
+      <c r="A185" s="39">
+        <v>46180</v>
+      </c>
       <c r="B185" s="27"/>
       <c r="C185" s="27"/>
-      <c r="D185" s="27"/>
+      <c r="D185" s="27" t="s">
+        <v>17</v>
+      </c>
       <c r="E185" s="42"/>
-      <c r="F185" s="42"/>
+      <c r="F185" s="42">
+        <v>2</v>
+      </c>
       <c r="G185" s="42">
         <f t="shared" ref="G185:G201" si="17">G184+E185-F185</f>
-        <v>203.25</v>
+        <v>184.25</v>
       </c>
       <c r="H185" s="27"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="39"/>
+      <c r="A186" s="39">
+        <v>46180</v>
+      </c>
       <c r="B186" s="27"/>
       <c r="C186" s="27"/>
-      <c r="D186" s="27"/>
+      <c r="D186" s="27" t="s">
+        <v>143</v>
+      </c>
       <c r="E186" s="42"/>
-      <c r="F186" s="42"/>
+      <c r="F186" s="42">
+        <v>1</v>
+      </c>
       <c r="G186" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>183.25</v>
       </c>
       <c r="H186" s="27"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="39"/>
+      <c r="A187" s="39">
+        <v>46181</v>
+      </c>
       <c r="B187" s="27"/>
       <c r="C187" s="27"/>
-      <c r="D187" s="27"/>
+      <c r="D187" s="27" t="s">
+        <v>76</v>
+      </c>
       <c r="E187" s="42"/>
-      <c r="F187" s="42"/>
+      <c r="F187" s="42">
+        <v>2.5</v>
+      </c>
       <c r="G187" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>180.75</v>
       </c>
       <c r="H187" s="27"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="39"/>
+      <c r="A188" s="39">
+        <v>46181</v>
+      </c>
       <c r="B188" s="27"/>
       <c r="C188" s="27"/>
-      <c r="D188" s="27"/>
+      <c r="D188" s="27" t="s">
+        <v>18</v>
+      </c>
       <c r="E188" s="42"/>
-      <c r="F188" s="42"/>
+      <c r="F188" s="42">
+        <v>2</v>
+      </c>
       <c r="G188" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>178.75</v>
       </c>
       <c r="H188" s="27"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="39"/>
+      <c r="A189" s="39">
+        <v>46182</v>
+      </c>
       <c r="B189" s="27"/>
       <c r="C189" s="27"/>
-      <c r="D189" s="27"/>
+      <c r="D189" s="27" t="s">
+        <v>505</v>
+      </c>
       <c r="E189" s="42"/>
-      <c r="F189" s="42"/>
+      <c r="F189" s="42">
+        <v>1</v>
+      </c>
       <c r="G189" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>177.75</v>
       </c>
       <c r="H189" s="27"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="39"/>
+      <c r="A190" s="39">
+        <v>46183</v>
+      </c>
       <c r="B190" s="27"/>
       <c r="C190" s="27"/>
-      <c r="D190" s="27"/>
+      <c r="D190" s="27" t="s">
+        <v>69</v>
+      </c>
       <c r="E190" s="42"/>
-      <c r="F190" s="42"/>
+      <c r="F190" s="42">
+        <v>0.6</v>
+      </c>
       <c r="G190" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>177.15</v>
       </c>
       <c r="H190" s="27"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="39"/>
+      <c r="A191" s="39">
+        <v>46183</v>
+      </c>
       <c r="B191" s="27"/>
       <c r="C191" s="27"/>
-      <c r="D191" s="27"/>
+      <c r="D191" s="27" t="s">
+        <v>293</v>
+      </c>
       <c r="E191" s="42"/>
-      <c r="F191" s="42"/>
+      <c r="F191" s="42">
+        <v>0.75</v>
+      </c>
       <c r="G191" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>176.4</v>
       </c>
       <c r="H191" s="27"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="39"/>
+      <c r="A192" s="39">
+        <v>46183</v>
+      </c>
       <c r="B192" s="27"/>
       <c r="C192" s="27"/>
-      <c r="D192" s="27"/>
+      <c r="D192" s="27" t="s">
+        <v>78</v>
+      </c>
       <c r="E192" s="42"/>
-      <c r="F192" s="42"/>
+      <c r="F192" s="42">
+        <v>0.75</v>
+      </c>
       <c r="G192" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>175.65</v>
       </c>
       <c r="H192" s="27"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="39"/>
+      <c r="A193" s="39">
+        <v>46183</v>
+      </c>
       <c r="B193" s="27"/>
       <c r="C193" s="27"/>
-      <c r="D193" s="27"/>
+      <c r="D193" s="27" t="s">
+        <v>156</v>
+      </c>
       <c r="E193" s="42"/>
-      <c r="F193" s="42"/>
+      <c r="F193" s="42">
+        <v>0.5</v>
+      </c>
       <c r="G193" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>175.15</v>
       </c>
       <c r="H193" s="27"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="39"/>
+      <c r="A194" s="39">
+        <v>46183</v>
+      </c>
       <c r="B194" s="27"/>
       <c r="C194" s="27"/>
-      <c r="D194" s="27"/>
+      <c r="D194" s="27" t="s">
+        <v>315</v>
+      </c>
       <c r="E194" s="42"/>
-      <c r="F194" s="42"/>
+      <c r="F194" s="42">
+        <v>2</v>
+      </c>
       <c r="G194" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>173.15</v>
       </c>
       <c r="H194" s="27"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="39"/>
+      <c r="A195" s="39">
+        <v>46183</v>
+      </c>
       <c r="B195" s="27"/>
       <c r="C195" s="27"/>
-      <c r="D195" s="27"/>
+      <c r="D195" s="27" t="s">
+        <v>72</v>
+      </c>
       <c r="E195" s="42"/>
-      <c r="F195" s="42"/>
+      <c r="F195" s="42">
+        <v>4.5</v>
+      </c>
       <c r="G195" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>168.65</v>
       </c>
       <c r="H195" s="27"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="39"/>
+      <c r="A196" s="39">
+        <v>46183</v>
+      </c>
       <c r="B196" s="27"/>
       <c r="C196" s="27"/>
-      <c r="D196" s="27"/>
+      <c r="D196" s="27" t="s">
+        <v>406</v>
+      </c>
       <c r="E196" s="42"/>
-      <c r="F196" s="42"/>
+      <c r="F196" s="42">
+        <v>1.6</v>
+      </c>
       <c r="G196" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H196" s="27"/>
     </row>
@@ -17798,7 +17920,7 @@
       <c r="F197" s="42"/>
       <c r="G197" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H197" s="27"/>
     </row>
@@ -17811,7 +17933,7 @@
       <c r="F198" s="42"/>
       <c r="G198" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H198" s="27"/>
     </row>
@@ -17824,7 +17946,7 @@
       <c r="F199" s="42"/>
       <c r="G199" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H199" s="27"/>
     </row>
@@ -17837,7 +17959,7 @@
       <c r="F200" s="42"/>
       <c r="G200" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H200" s="27"/>
     </row>
@@ -17850,7 +17972,7 @@
       <c r="F201" s="42"/>
       <c r="G201" s="42">
         <f t="shared" si="17"/>
-        <v>203.25</v>
+        <v>167.05</v>
       </c>
       <c r="H201" s="27"/>
     </row>
@@ -17862,7 +17984,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K324"/>
+  <dimension ref="A1:K329"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="57" customWidth="1"/>
@@ -23294,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="G289" s="62">
-        <f t="shared" ref="G289:G324" si="13">G288+E289-F289</f>
+        <f t="shared" ref="G289:G329" si="13">G288+E289-F289</f>
         <v>5.25</v>
       </c>
       <c r="H289" s="59"/>
@@ -23875,69 +23997,154 @@
       <c r="H319" s="59"/>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" s="60"/>
+      <c r="A320" s="60">
+        <v>46180</v>
+      </c>
       <c r="B320" s="59"/>
       <c r="C320" s="59"/>
-      <c r="D320" s="69"/>
+      <c r="D320" s="69" t="s">
+        <v>531</v>
+      </c>
       <c r="E320" s="62"/>
-      <c r="F320" s="62"/>
+      <c r="F320" s="62">
+        <v>0.25</v>
+      </c>
       <c r="G320" s="62">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H320" s="59"/>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" s="60"/>
+      <c r="A321" s="60">
+        <v>46181</v>
+      </c>
       <c r="B321" s="59"/>
       <c r="C321" s="59"/>
-      <c r="D321" s="69"/>
+      <c r="D321" s="69" t="s">
+        <v>144</v>
+      </c>
       <c r="E321" s="62"/>
-      <c r="F321" s="62"/>
+      <c r="F321" s="62">
+        <v>1</v>
+      </c>
       <c r="G321" s="62">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="H321" s="59"/>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" s="60"/>
+      <c r="A322" s="60">
+        <v>46183</v>
+      </c>
       <c r="B322" s="59"/>
       <c r="C322" s="59"/>
-      <c r="D322" s="69"/>
+      <c r="D322" s="69" t="s">
+        <v>69</v>
+      </c>
       <c r="E322" s="62"/>
-      <c r="F322" s="62"/>
+      <c r="F322" s="62">
+        <v>1</v>
+      </c>
       <c r="G322" s="62">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="H322" s="59"/>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" s="60"/>
+      <c r="A323" s="60">
+        <v>46183</v>
+      </c>
       <c r="B323" s="59"/>
       <c r="C323" s="59"/>
-      <c r="D323" s="69"/>
+      <c r="D323" s="69" t="s">
+        <v>69</v>
+      </c>
       <c r="E323" s="62"/>
-      <c r="F323" s="62"/>
+      <c r="F323" s="62">
+        <v>0.5</v>
+      </c>
       <c r="G323" s="62">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="H323" s="59"/>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" s="60"/>
+      <c r="A324" s="60">
+        <v>46184</v>
+      </c>
       <c r="B324" s="59"/>
       <c r="C324" s="59"/>
-      <c r="D324" s="69"/>
+      <c r="D324" s="69" t="s">
+        <v>147</v>
+      </c>
       <c r="E324" s="62"/>
-      <c r="F324" s="62"/>
+      <c r="F324" s="62">
+        <v>0.25</v>
+      </c>
       <c r="G324" s="62">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H324" s="59"/>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A325" s="60"/>
+      <c r="B325" s="59"/>
+      <c r="C325" s="59"/>
+      <c r="D325" s="69"/>
+      <c r="E325" s="62"/>
+      <c r="F325" s="62"/>
+      <c r="G325" s="62">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H325" s="59"/>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A326" s="60"/>
+      <c r="B326" s="59"/>
+      <c r="C326" s="59"/>
+      <c r="D326" s="69"/>
+      <c r="E326" s="62"/>
+      <c r="F326" s="62"/>
+      <c r="G326" s="62">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H326" s="59"/>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A327" s="60"/>
+      <c r="B327" s="59"/>
+      <c r="C327" s="59"/>
+      <c r="D327" s="69"/>
+      <c r="E327" s="62"/>
+      <c r="F327" s="62"/>
+      <c r="G327" s="62">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H327" s="59"/>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A328" s="60"/>
+      <c r="B328" s="59"/>
+      <c r="C328" s="59"/>
+      <c r="D328" s="69"/>
+      <c r="E328" s="62"/>
+      <c r="F328" s="62"/>
+      <c r="G328" s="62">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H328" s="59"/>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G329" s="62"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:H131"/>
@@ -24173,15 +24380,21 @@
       <c r="H15" s="59"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="60"/>
+      <c r="A16" s="60">
+        <v>46181</v>
+      </c>
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
+      <c r="D16" s="59" t="s">
+        <v>533</v>
+      </c>
       <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
+      <c r="F16" s="62">
+        <v>0.25</v>
+      </c>
       <c r="G16" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H16" s="59"/>
     </row>
@@ -24194,7 +24407,7 @@
       <c r="F17" s="62"/>
       <c r="G17" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H17" s="59"/>
     </row>
@@ -24207,7 +24420,7 @@
       <c r="F18" s="62"/>
       <c r="G18" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H18" s="59"/>
     </row>
@@ -24220,7 +24433,7 @@
       <c r="F19" s="62"/>
       <c r="G19" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H19" s="59"/>
     </row>
@@ -24233,7 +24446,7 @@
       <c r="F20" s="62"/>
       <c r="G20" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H20" s="59"/>
     </row>
@@ -24246,7 +24459,7 @@
       <c r="F21" s="62"/>
       <c r="G21" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H21" s="59"/>
     </row>
@@ -24259,7 +24472,7 @@
       <c r="F22" s="73"/>
       <c r="G22" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H22" s="72"/>
     </row>
@@ -24272,7 +24485,7 @@
       <c r="F23" s="62"/>
       <c r="G23" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H23" s="59"/>
     </row>
@@ -24285,7 +24498,7 @@
       <c r="F24" s="62"/>
       <c r="G24" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H24" s="59"/>
     </row>
@@ -24298,7 +24511,7 @@
       <c r="F25" s="62"/>
       <c r="G25" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H25" s="59"/>
     </row>
@@ -24311,7 +24524,7 @@
       <c r="F26" s="62"/>
       <c r="G26" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H26" s="59"/>
     </row>
@@ -24324,7 +24537,7 @@
       <c r="F27" s="62"/>
       <c r="G27" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H27" s="59"/>
     </row>
@@ -24337,7 +24550,7 @@
       <c r="F28" s="62"/>
       <c r="G28" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H28" s="59"/>
     </row>
@@ -24350,7 +24563,7 @@
       <c r="F29" s="62"/>
       <c r="G29" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H29" s="59"/>
     </row>
@@ -24363,7 +24576,7 @@
       <c r="F30" s="62"/>
       <c r="G30" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H30" s="59"/>
     </row>
@@ -24376,7 +24589,7 @@
       <c r="F31" s="73"/>
       <c r="G31" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H31" s="72"/>
     </row>
@@ -24389,7 +24602,7 @@
       <c r="F32" s="62"/>
       <c r="G32" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H32" s="59"/>
     </row>
@@ -24402,7 +24615,7 @@
       <c r="F33" s="62"/>
       <c r="G33" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H33" s="59"/>
     </row>
@@ -24415,7 +24628,7 @@
       <c r="F34" s="62"/>
       <c r="G34" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H34" s="59"/>
     </row>
@@ -24428,7 +24641,7 @@
       <c r="F35" s="62"/>
       <c r="G35" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H35" s="59"/>
     </row>
@@ -24441,7 +24654,7 @@
       <c r="F36" s="62"/>
       <c r="G36" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H36" s="59"/>
     </row>
@@ -24454,7 +24667,7 @@
       <c r="F37" s="62"/>
       <c r="G37" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H37" s="59"/>
     </row>
@@ -24467,7 +24680,7 @@
       <c r="F38" s="62"/>
       <c r="G38" s="62">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H38" s="59"/>
     </row>
@@ -24480,7 +24693,7 @@
       <c r="F39" s="73"/>
       <c r="G39" s="73">
         <f t="shared" si="0"/>
-        <v>1.1499999999999999</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="H39" s="72"/>
     </row>
@@ -29763,57 +29976,81 @@
       <c r="I260" s="57"/>
     </row>
     <row r="261" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A261" s="68"/>
+      <c r="A261" s="68">
+        <v>46180</v>
+      </c>
       <c r="B261" s="59"/>
       <c r="C261" s="59"/>
-      <c r="D261" s="59"/>
+      <c r="D261" s="59" t="s">
+        <v>83</v>
+      </c>
       <c r="E261" s="62"/>
-      <c r="F261" s="62"/>
+      <c r="F261" s="62">
+        <v>0.5</v>
+      </c>
       <c r="G261" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>204.75</v>
       </c>
       <c r="H261" s="62"/>
       <c r="I261" s="57"/>
     </row>
     <row r="262" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A262" s="68"/>
+      <c r="A262" s="68">
+        <v>46182</v>
+      </c>
       <c r="B262" s="59"/>
       <c r="C262" s="59"/>
-      <c r="D262" s="59"/>
+      <c r="D262" s="59" t="s">
+        <v>433</v>
+      </c>
       <c r="E262" s="62"/>
-      <c r="F262" s="62"/>
+      <c r="F262" s="62">
+        <v>1</v>
+      </c>
       <c r="G262" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>203.75</v>
       </c>
       <c r="H262" s="62"/>
       <c r="I262" s="57"/>
     </row>
     <row r="263" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A263" s="68"/>
+      <c r="A263" s="68">
+        <v>46183</v>
+      </c>
       <c r="B263" s="59"/>
       <c r="C263" s="59"/>
-      <c r="D263" s="59"/>
+      <c r="D263" s="59" t="s">
+        <v>535</v>
+      </c>
       <c r="E263" s="62"/>
-      <c r="F263" s="62"/>
+      <c r="F263" s="62">
+        <v>0.75</v>
+      </c>
       <c r="G263" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>203</v>
       </c>
       <c r="H263" s="62"/>
       <c r="I263" s="57"/>
     </row>
     <row r="264" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A264" s="68"/>
+      <c r="A264" s="68">
+        <v>46184</v>
+      </c>
       <c r="B264" s="59"/>
       <c r="C264" s="59"/>
-      <c r="D264" s="59"/>
+      <c r="D264" s="59" t="s">
+        <v>134</v>
+      </c>
       <c r="E264" s="62"/>
-      <c r="F264" s="62"/>
+      <c r="F264" s="62">
+        <v>20</v>
+      </c>
       <c r="G264" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H264" s="62"/>
       <c r="I264" s="57"/>
@@ -29827,7 +30064,7 @@
       <c r="F265" s="62"/>
       <c r="G265" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H265" s="62"/>
       <c r="I265" s="57"/>
@@ -29841,7 +30078,7 @@
       <c r="F266" s="62"/>
       <c r="G266" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H266" s="62"/>
       <c r="I266" s="57"/>
@@ -29855,7 +30092,7 @@
       <c r="F267" s="62"/>
       <c r="G267" s="80">
         <f t="shared" si="10"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H267" s="62"/>
       <c r="I267" s="57"/>
@@ -29869,7 +30106,7 @@
       <c r="F268" s="62"/>
       <c r="G268" s="80">
         <f t="shared" ref="G268:G277" si="11">G267+E268-F268</f>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H268" s="62"/>
       <c r="I268" s="57"/>
@@ -29883,7 +30120,7 @@
       <c r="F269" s="62"/>
       <c r="G269" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H269" s="62"/>
       <c r="I269" s="57"/>
@@ -29897,7 +30134,7 @@
       <c r="F270" s="62"/>
       <c r="G270" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H270" s="62"/>
       <c r="I270" s="57"/>
@@ -29911,7 +30148,7 @@
       <c r="F271" s="62"/>
       <c r="G271" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H271" s="62"/>
       <c r="I271" s="57"/>
@@ -29925,7 +30162,7 @@
       <c r="F272" s="62"/>
       <c r="G272" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H272" s="62"/>
       <c r="I272" s="57"/>
@@ -29939,7 +30176,7 @@
       <c r="F273" s="62"/>
       <c r="G273" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H273" s="62"/>
       <c r="I273" s="57"/>
@@ -29953,7 +30190,7 @@
       <c r="F274" s="62"/>
       <c r="G274" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H274" s="62"/>
       <c r="I274" s="57"/>
@@ -29967,7 +30204,7 @@
       <c r="F275" s="62"/>
       <c r="G275" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H275" s="62"/>
       <c r="I275" s="57"/>
@@ -29981,7 +30218,7 @@
       <c r="F276" s="62"/>
       <c r="G276" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H276" s="62"/>
       <c r="I276" s="57"/>
@@ -29995,7 +30232,7 @@
       <c r="F277" s="62"/>
       <c r="G277" s="80">
         <f t="shared" si="11"/>
-        <v>205.25</v>
+        <v>183</v>
       </c>
       <c r="H277" s="62"/>
       <c r="I277" s="57"/>
@@ -30202,15 +30439,21 @@
       <c r="H13" s="59"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
+      <c r="A14" s="60">
+        <v>46181</v>
+      </c>
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
+      <c r="D14" s="59" t="s">
+        <v>320</v>
+      </c>
       <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
+      <c r="F14" s="62">
+        <v>0.5</v>
+      </c>
       <c r="G14" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H14" s="59"/>
     </row>
@@ -30223,7 +30466,7 @@
       <c r="F15" s="62"/>
       <c r="G15" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="59"/>
     </row>
@@ -30236,7 +30479,7 @@
       <c r="F16" s="62"/>
       <c r="G16" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="59"/>
     </row>
@@ -30249,7 +30492,7 @@
       <c r="F17" s="62"/>
       <c r="G17" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="59"/>
     </row>
@@ -30262,7 +30505,7 @@
       <c r="F18" s="62"/>
       <c r="G18" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="59"/>
     </row>
@@ -30275,7 +30518,7 @@
       <c r="F19" s="62"/>
       <c r="G19" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="59"/>
     </row>
@@ -30288,7 +30531,7 @@
       <c r="F20" s="62"/>
       <c r="G20" s="62">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="59"/>
     </row>
@@ -30304,7 +30547,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
@@ -30722,129 +30965,191 @@
       <c r="H25" s="1"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1">
+      <c r="A26" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B26" s="2">
+        <v>142348</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E26" s="2">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="A27" s="3">
+        <v>46161</v>
+      </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
       <c r="G27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H27" s="1"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="3">
+        <v>46162</v>
+      </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1">
+        <v>1.5</v>
+      </c>
       <c r="G28" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H28" s="1"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+      <c r="A29" s="3">
+        <v>46163</v>
+      </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1">
+        <v>2</v>
+      </c>
       <c r="G29" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="3">
+        <v>46164</v>
+      </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1">
+        <v>0.75</v>
+      </c>
       <c r="G30" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="A31" s="3">
+        <v>46165</v>
+      </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1">
+        <v>1.25</v>
+      </c>
       <c r="G31" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+      <c r="A32" s="3">
+        <v>46166</v>
+      </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1">
+        <v>0.75</v>
+      </c>
       <c r="G32" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="H32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+      <c r="A33" s="3">
+        <v>46167</v>
+      </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="1">
+        <v>1.25</v>
+      </c>
       <c r="G33" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+      <c r="A34" s="3">
+        <v>46168</v>
+      </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
       <c r="G34" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+      <c r="A35" s="3">
+        <v>46169</v>
+      </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1">
+        <v>0.5</v>
+      </c>
       <c r="G35" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -30852,30 +31157,357 @@
       <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
+      <c r="A36" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B36" s="2">
+        <v>142348</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E36" s="2">
+        <v>6</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+      <c r="A37" s="3">
+        <v>46170</v>
+      </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>497</v>
+      </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1">
+        <v>0.5</v>
+      </c>
       <c r="G37" s="1">
         <f t="shared" si="1"/>
+        <v>5.5</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" ref="G38:G48" si="2">G37+E38-F38</f>
+        <v>4.75</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46172</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="2"/>
+        <v>3.25</v>
+      </c>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>46173</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G40" s="1">
+        <f t="shared" si="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <f t="shared" si="2"/>
+        <v>1.75</v>
+      </c>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="G42" s="1">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B43" s="2">
+        <v>166963</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E43" s="2">
+        <v>6</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>46179</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>46180</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G48" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1">
+        <f t="shared" ref="G49:G55" si="3">G48+E49-F49</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="M50" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31489,98 +32121,98 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="159" t="s">
+      <c r="A3" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="160"/>
+      <c r="B3" s="157"/>
       <c r="C3" s="161"/>
       <c r="D3" s="162"/>
-      <c r="E3" s="159" t="s">
+      <c r="E3" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="F3" s="160"/>
+      <c r="F3" s="157"/>
       <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="150"/>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="153"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="152"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="150"/>
-      <c r="B5" s="151"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
+      <c r="A5" s="152"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="150"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="151"/>
+      <c r="A6" s="152"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="152"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="150"/>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="151"/>
-      <c r="G7" s="151"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="150"/>
-      <c r="B8" s="151"/>
-      <c r="C8" s="151"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
+      <c r="A8" s="152"/>
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="150"/>
-      <c r="B9" s="151"/>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="151"/>
+      <c r="A9" s="152"/>
+      <c r="B9" s="153"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="156"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
+      <c r="A10" s="150"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="151"/>
       <c r="D10" s="158"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="157"/>
+      <c r="E10" s="150"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="151"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="150"/>
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="151"/>
+      <c r="A11" s="152"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="152"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="153"/>
-      <c r="B12" s="154"/>
-      <c r="C12" s="154"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="154"/>
-      <c r="G12" s="154"/>
+      <c r="A12" s="154"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="155"/>
+      <c r="G12" s="155"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
@@ -31657,98 +32289,98 @@
       <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="159" t="s">
+      <c r="A19" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="160"/>
+      <c r="B19" s="157"/>
       <c r="C19" s="161"/>
       <c r="D19" s="162"/>
-      <c r="E19" s="159" t="s">
+      <c r="E19" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="F19" s="160"/>
+      <c r="F19" s="157"/>
       <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="150"/>
-      <c r="B20" s="151"/>
-      <c r="C20" s="151"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="151"/>
-      <c r="G20" s="151"/>
+      <c r="A20" s="152"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="159"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="150"/>
-      <c r="B21" s="151"/>
-      <c r="C21" s="151"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="151"/>
-      <c r="G21" s="151"/>
+      <c r="A21" s="152"/>
+      <c r="B21" s="153"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="159"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="150"/>
-      <c r="B22" s="151"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="151"/>
-      <c r="G22" s="151"/>
+      <c r="A22" s="152"/>
+      <c r="B22" s="153"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="159"/>
+      <c r="E22" s="152"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="150"/>
-      <c r="B23" s="151"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="151"/>
-      <c r="G23" s="151"/>
+      <c r="A23" s="152"/>
+      <c r="B23" s="153"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="150"/>
-      <c r="B24" s="151"/>
-      <c r="C24" s="151"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="151"/>
-      <c r="G24" s="151"/>
+      <c r="A24" s="152"/>
+      <c r="B24" s="153"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="150"/>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151"/>
+      <c r="A25" s="152"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="156"/>
-      <c r="B26" s="157"/>
-      <c r="C26" s="157"/>
+      <c r="A26" s="150"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="151"/>
       <c r="D26" s="158"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="157"/>
-      <c r="G26" s="157"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="150"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
+      <c r="A27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="159"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="153"/>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
+      <c r="A28" s="154"/>
+      <c r="B28" s="155"/>
+      <c r="C28" s="155"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="155"/>
+      <c r="G28" s="155"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
@@ -31817,98 +32449,98 @@
       <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="159" t="s">
+      <c r="A35" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="B35" s="160"/>
+      <c r="B35" s="157"/>
       <c r="C35" s="161"/>
       <c r="D35" s="162"/>
-      <c r="E35" s="159" t="s">
+      <c r="E35" s="156" t="s">
         <v>282</v>
       </c>
-      <c r="F35" s="160"/>
+      <c r="F35" s="157"/>
       <c r="G35" s="26"/>
     </row>
     <row r="36" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="150"/>
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="150"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
+      <c r="A36" s="152"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="159"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="153"/>
     </row>
     <row r="37" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="150"/>
-      <c r="B37" s="151"/>
-      <c r="C37" s="151"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="150"/>
-      <c r="F37" s="151"/>
-      <c r="G37" s="151"/>
+      <c r="A37" s="152"/>
+      <c r="B37" s="153"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="159"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="153"/>
     </row>
     <row r="38" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="150"/>
-      <c r="B38" s="151"/>
-      <c r="C38" s="151"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="150"/>
-      <c r="F38" s="151"/>
-      <c r="G38" s="151"/>
+      <c r="A38" s="152"/>
+      <c r="B38" s="153"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="159"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="153"/>
+      <c r="G38" s="153"/>
     </row>
     <row r="39" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="150"/>
-      <c r="B39" s="151"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="150"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
+      <c r="A39" s="152"/>
+      <c r="B39" s="153"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="159"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="153"/>
     </row>
     <row r="40" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="150"/>
-      <c r="B40" s="151"/>
-      <c r="C40" s="151"/>
-      <c r="D40" s="152"/>
-      <c r="E40" s="150"/>
-      <c r="F40" s="151"/>
-      <c r="G40" s="151"/>
+      <c r="A40" s="152"/>
+      <c r="B40" s="153"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="159"/>
+      <c r="E40" s="152"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="153"/>
     </row>
     <row r="41" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="150"/>
-      <c r="B41" s="151"/>
-      <c r="C41" s="151"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="150"/>
-      <c r="F41" s="151"/>
-      <c r="G41" s="151"/>
+      <c r="A41" s="152"/>
+      <c r="B41" s="153"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="159"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="153"/>
     </row>
     <row r="42" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="156"/>
-      <c r="B42" s="157"/>
-      <c r="C42" s="157"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="158"/>
-      <c r="E42" s="156"/>
-      <c r="F42" s="157"/>
-      <c r="G42" s="157"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="151"/>
+      <c r="G42" s="151"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="150"/>
-      <c r="B43" s="151"/>
-      <c r="C43" s="151"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="151"/>
-      <c r="G43" s="151"/>
+      <c r="A43" s="152"/>
+      <c r="B43" s="153"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="159"/>
+      <c r="E43" s="152"/>
+      <c r="F43" s="153"/>
+      <c r="G43" s="153"/>
     </row>
     <row r="44" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="153"/>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="155"/>
-      <c r="E44" s="153"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="154"/>
+      <c r="A44" s="154"/>
+      <c r="B44" s="155"/>
+      <c r="C44" s="155"/>
+      <c r="D44" s="160"/>
+      <c r="E44" s="154"/>
+      <c r="F44" s="155"/>
+      <c r="G44" s="155"/>
     </row>
     <row r="45" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20" t="s">
@@ -31951,16 +32583,48 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A28:D28"/>
@@ -31972,48 +32636,16 @@
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41248,41 +41880,61 @@
       <c r="H305" s="59"/>
     </row>
     <row r="306" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A306" s="60"/>
+      <c r="A306" s="60">
+        <v>46180</v>
+      </c>
       <c r="B306" s="59"/>
       <c r="C306" s="59"/>
-      <c r="D306" s="59"/>
+      <c r="D306" s="59" t="s">
+        <v>134</v>
+      </c>
       <c r="E306" s="62"/>
-      <c r="F306" s="62"/>
+      <c r="F306" s="62">
+        <v>60</v>
+      </c>
       <c r="G306" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>63.25</v>
       </c>
       <c r="H306" s="59"/>
     </row>
     <row r="307" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A307" s="60"/>
+      <c r="A307" s="60">
+        <v>46180</v>
+      </c>
       <c r="B307" s="59"/>
       <c r="C307" s="59"/>
-      <c r="D307" s="59"/>
+      <c r="D307" s="59" t="s">
+        <v>532</v>
+      </c>
       <c r="E307" s="62"/>
-      <c r="F307" s="62"/>
+      <c r="F307" s="62">
+        <v>10</v>
+      </c>
       <c r="G307" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>53.25</v>
       </c>
       <c r="H307" s="59"/>
     </row>
     <row r="308" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A308" s="60"/>
+      <c r="A308" s="60">
+        <v>46182</v>
+      </c>
       <c r="B308" s="59"/>
-      <c r="C308" s="59"/>
-      <c r="D308" s="59"/>
+      <c r="C308" s="59">
+        <v>64481</v>
+      </c>
+      <c r="D308" s="59" t="s">
+        <v>534</v>
+      </c>
       <c r="E308" s="62"/>
-      <c r="F308" s="62"/>
+      <c r="F308" s="62">
+        <v>20</v>
+      </c>
       <c r="G308" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="H308" s="59"/>
     </row>
@@ -41295,7 +41947,7 @@
       <c r="F309" s="62"/>
       <c r="G309" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="H309" s="59"/>
     </row>
@@ -41308,7 +41960,7 @@
       <c r="F310" s="62"/>
       <c r="G310" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="H310" s="59"/>
     </row>
@@ -41321,7 +41973,7 @@
       <c r="F311" s="62"/>
       <c r="G311" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="H311" s="59"/>
     </row>
@@ -41334,7 +41986,7 @@
       <c r="F312" s="62"/>
       <c r="G312" s="62">
         <f t="shared" si="24"/>
-        <v>123.25</v>
+        <v>33.25</v>
       </c>
       <c r="H312" s="59"/>
     </row>
